--- a/data/empresas/Db Terra Chile Holdco SpA/temp_uploaded.xlsx
+++ b/data/empresas/Db Terra Chile Holdco SpA/temp_uploaded.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mundo\2026\Agosto 2026\Holdco\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mundo\Programa de informes\Test de carga Holco\Agosto 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABBFC857-994D-419E-AE9F-491BAE9026C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4944800-CEA5-495E-A63E-E1DC96D5500E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{42D6E0A4-7165-445E-A254-3F135233587D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E36B15BE-C11D-4568-A1A8-4D1BEE6E6712}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -62,25 +62,25 @@
     <t>BANCO BCI CL</t>
   </si>
   <si>
-    <t>BANCO BCI USD</t>
-  </si>
-  <si>
-    <t>BANCO BCI EUR</t>
-  </si>
-  <si>
-    <t>BANCO SCOTIABANK CL</t>
-  </si>
-  <si>
-    <t>BANCO SCOTIABANK USD</t>
-  </si>
-  <si>
-    <t>BANCO JP MORGAN US$</t>
-  </si>
-  <si>
-    <t>Cuenta transitoria BANCO SCOTIABANK CL</t>
-  </si>
-  <si>
-    <t>Cuenta transitoria BANCO SCOTIABANK USD</t>
+    <t xml:space="preserve">BANCO BCI USD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANCO BCI EUR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANCO SCOTIABANK CL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANCO SCOTIABANK USD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANCO JP MORGAN US$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuenta transitoria BANCO SCOTIABANK CL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuenta transitoria BANCO SCOTIABANK USD </t>
   </si>
   <si>
     <t>ABONOS BANCO BCI CL</t>
@@ -89,34 +89,34 @@
     <t>CARGOS BANCO BCI CL</t>
   </si>
   <si>
-    <t>ABONOS BANCO BCI USD</t>
-  </si>
-  <si>
-    <t>CARGOS BANCO BCI USD</t>
-  </si>
-  <si>
-    <t>ABONOS BANCO BCI EUR</t>
-  </si>
-  <si>
-    <t>CARGOS BANCO BCI EUR</t>
-  </si>
-  <si>
-    <t>ABONOS BANCO SCOTIABANK CL</t>
-  </si>
-  <si>
-    <t>CARGOS BANCO SCOTIABANK CL</t>
-  </si>
-  <si>
-    <t>ABONOS BANCO SCOTIABANK USD</t>
-  </si>
-  <si>
-    <t>CARGOS BANCO SCOTIABANK USD</t>
-  </si>
-  <si>
-    <t>ABONOS BANCO JP MORGAN US$</t>
-  </si>
-  <si>
-    <t>CARGOS BANCO JP MORGAN US$</t>
+    <t xml:space="preserve">ABONOS BANCO BCI USD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARGOS BANCO BCI USD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABONOS BANCO BCI EUR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARGOS BANCO BCI EUR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABONOS BANCO SCOTIABANK CL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARGOS BANCO SCOTIABANK CL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABONOS BANCO SCOTIABANK USD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARGOS BANCO SCOTIABANK USD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABONOS BANCO JP MORGAN US$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARGOS BANCO JP MORGAN US$ </t>
   </si>
   <si>
     <t>CUENTA TRANSFERENCIA INTERNA</t>
@@ -200,7 +200,7 @@
     <t>FONDOS POR RENDIR</t>
   </si>
   <si>
-    <t>GASTOS ANTICIPADOS</t>
+    <t xml:space="preserve">GASTOS ANTICIPADOS </t>
   </si>
   <si>
     <t>ANTICIPO ARRIENDOS</t>
@@ -215,7 +215,8 @@
     <t>OTROS DEUDORES</t>
   </si>
   <si>
-    <t>ANTICIPO PROVEEDORES EXTRANJEROS YUAN</t>
+    <t xml:space="preserve">ANTICIPO PROVEEDORES EXTRANJEROS YUAN 
+</t>
   </si>
   <si>
     <t>MERCADERIA EN TRANSITO EURO</t>
@@ -299,7 +300,7 @@
     <t>MATERIALES IMPORTADOS</t>
   </si>
   <si>
-    <t>AJUSTES INVENTARIOS BODEGAS</t>
+    <t xml:space="preserve">AJUSTES INVENTARIOS BODEGAS </t>
   </si>
   <si>
     <t>MATERIALES EN TRANSITO</t>
@@ -413,19 +414,19 @@
     <t>DEPRECIACION ACUMULADA CONSTRUCCIONES Y OBRAS</t>
   </si>
   <si>
-    <t>DEPRECIACION ACUMULADA REDES DE TRANSMISION</t>
+    <t xml:space="preserve">DEPRECIACION ACUMULADA REDES DE TRANSMISION			</t>
   </si>
   <si>
     <t>DEPRECIACION ACUMULADA EQUIPOS COMPUTACIONALES</t>
   </si>
   <si>
-    <t>DEPRECIACION ACUMULADA MUEBLES Y UTILES</t>
-  </si>
-  <si>
-    <t>DEPRECIACION ACUMULADA VEHICULOS</t>
-  </si>
-  <si>
-    <t>DEPRECIACION ACUMULADA OTROS ACTIVOS FIJOS</t>
+    <t xml:space="preserve">DEPRECIACION ACUMULADA MUEBLES Y UTILES			</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEPRECIACION ACUMULADA VEHICULOS			</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEPRECIACION ACUMULADA OTROS ACTIVOS FIJOS			</t>
   </si>
   <si>
     <t>DEPRECIACION ACUMULADA PLANTA TRANSMISORA</t>
@@ -845,7 +846,7 @@
     <t>OTRAS RESERVAS DERIVADOS BONO 144A</t>
   </si>
   <si>
-    <t>INGRESOS ARRIENDO FIBRA OPTICA</t>
+    <t>INGRESOS ARRIENDO FIBRA OPTICA </t>
   </si>
   <si>
     <t>SERVICIOS DE CONSTRUCCION</t>
@@ -1013,7 +1014,7 @@
     <t>MULTAS E INTERESES</t>
   </si>
   <si>
-    <t>SEGUROS, INMUEBLES Y OTROS</t>
+    <t xml:space="preserve">SEGUROS, INMUEBLES Y OTROS			</t>
   </si>
   <si>
     <t>PERMISOS MUNICIPALES</t>
@@ -1025,7 +1026,7 @@
     <t>GASTO MANTENCION Y REPARACION EQUIPOS</t>
   </si>
   <si>
-    <t>MATERIALES</t>
+    <t xml:space="preserve">MATERIALES </t>
   </si>
   <si>
     <t>INSUMOS (RESULTADO)</t>
@@ -1672,13 +1673,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C12D046-1E61-4F13-9837-1B33B8EF4E94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DFB8282-E8C8-40FF-B80E-5FC0488F8A32}">
   <dimension ref="A1:C402"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="77" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -4636,7 +4633,7 @@
         <v>270</v>
       </c>
       <c r="C269" s="4">
-        <v>-362654577</v>
+        <v>-356532000</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
@@ -4680,7 +4677,7 @@
         <v>274</v>
       </c>
       <c r="C273" s="4">
-        <v>-72423348</v>
+        <v>-66692022</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
@@ -4691,7 +4688,7 @@
         <v>275</v>
       </c>
       <c r="C274" s="4">
-        <v>-52810941170</v>
+        <v>-52822795073</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
@@ -4713,7 +4710,7 @@
         <v>277</v>
       </c>
       <c r="C276" s="4">
-        <v>-1340237901</v>
+        <v>-1343528198</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
@@ -5153,7 +5150,7 @@
         <v>317</v>
       </c>
       <c r="C316" s="4">
-        <v>45160980</v>
+        <v>48451277</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
